--- a/scrubbing_process/Batch # 1 - $119,802.46_5rows_scrubbed.xlsx
+++ b/scrubbing_process/Batch # 1 - $119,802.46_5rows_scrubbed.xlsx
@@ -28256,7 +28256,7 @@
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="33" customWidth="1" min="5" max="5"/>
-    <col width="38" customWidth="1" min="6" max="6"/>
+    <col width="37" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="34" customWidth="1" min="8" max="8"/>
     <col width="34" customWidth="1" min="9" max="9"/>
@@ -28281,7 +28281,7 @@
     <col width="28" customWidth="1" min="28" max="28"/>
     <col width="18" customWidth="1" min="29" max="29"/>
     <col width="50" customWidth="1" min="30" max="30"/>
-    <col width="50" customWidth="1" min="31" max="31"/>
+    <col width="47" customWidth="1" min="31" max="31"/>
     <col width="17" customWidth="1" min="32" max="32"/>
     <col width="13" customWidth="1" min="33" max="33"/>
   </cols>
@@ -28472,9 +28472,9 @@
       <c r="E2" s="3" t="n">
         <v>46064</v>
       </c>
-      <c r="F2" s="5" t="inlineStr">
-        <is>
-          <t>Refund/RT: JFK-SLC/Strategy Mtg</t>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Refund/RT: JFK-SLC/Strategy</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
@@ -28517,22 +28517,22 @@
       </c>
       <c r="P2" s="6" t="inlineStr">
         <is>
-          <t>Desc: Refund/RT: JFK-SLC/Strategy =&gt; Refund/RT: JFK-SLC/Strategy Mtg | PayType: American Express Corporate Card CBCP =&gt; American Express</t>
+          <t>PayType: American Express Corporate Card CBCP =&gt; American Express</t>
         </is>
       </c>
       <c r="Q2" s="6" t="inlineStr">
         <is>
-          <t>Refund format preserved; route present, but purpose/deal appears truncated vs original travel context. Prepaid project review applies.</t>
+          <t>Refund format preserved; original description mirrors flight route and purpose. Project 1035 noted prepaid, but no posting-time code change needed here.</t>
         </is>
       </c>
       <c r="R2" s="6" t="inlineStr">
         <is>
-          <t>Prepaid project - review G/L 14000 at posting | Refund description may be incomplete vs original charge | Prepaid project - review G/L 14000 at posting</t>
+          <t>Prepaid project - review G/L 14000 at posting | Prepaid project - review G/L 14000 at posting</t>
         </is>
       </c>
       <c r="S2" s="6" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="T2">
@@ -28576,16 +28576,16 @@
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.78</v>
+        <v>0.96</v>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>Refund format preserved; route present, but purpose/deal appears truncated vs original travel context. Prepaid project review applies.</t>
+          <t>Refund format preserved; original description mirrors flight route and purpose. Project 1035 noted prepaid, but no posting-time code change needed here.</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>Prepaid project - review G/L 14000 at posting | Refund description may be incomplete vs original charge</t>
+          <t>Prepaid project - review G/L 14000 at posting</t>
         </is>
       </c>
       <c r="AF2" t="b">
@@ -28662,13 +28662,13 @@
       </c>
       <c r="Q3" s="6" t="inlineStr">
         <is>
-          <t>Refund format is compliant; purpose/deal preserved and already in scrubbed style.</t>
+          <t>Refund format is valid and complete; route, purpose, and deal/company preserved.</t>
         </is>
       </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" s="6" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="T3">
@@ -28712,11 +28712,11 @@
         <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.86</v>
+        <v>0.97</v>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>Refund format is compliant; purpose/deal preserved and already in scrubbed style.</t>
+          <t>Refund format is valid and complete; route, purpose, and deal/company preserved.</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr"/>
@@ -28794,17 +28794,17 @@
       </c>
       <c r="Q4" s="6" t="inlineStr">
         <is>
-          <t>Looks like a meal deposit/advance, but description does not match a standard meal template and needs human review.</t>
+          <t>Description kept as-is; appears to be a deposit for BOD Dinner. Meal type is plausible but not enough detail to reclassify with confidence.</t>
         </is>
       </c>
       <c r="R4" s="6" t="inlineStr">
         <is>
-          <t>Description missing clear business meal format | Possible deposit/advance requires review</t>
+          <t>Low confidence descriptions</t>
         </is>
       </c>
       <c r="S4" s="6" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="T4">
@@ -28828,7 +28828,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>meal_business</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -28848,16 +28848,16 @@
         <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.67</v>
+        <v>0.78</v>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>Looks like a meal deposit/advance, but description does not match a standard meal template and needs human review.</t>
+          <t>Description kept as-is; appears to be a deposit for BOD Dinner. Meal type is plausible but not enough detail to reclassify with confidence.</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>Description missing clear business meal format | Possible deposit/advance requires review</t>
+          <t>Low confidence descriptions</t>
         </is>
       </c>
       <c r="AF4" t="b">
@@ -28934,13 +28934,13 @@
       </c>
       <c r="Q5" s="6" t="inlineStr">
         <is>
-          <t>Flight format compliant; route, purpose, and company preserved.</t>
+          <t>Flight description is compliant; Mgmt abbreviation is valid and route/purpose/deal are preserved.</t>
         </is>
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" s="6" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="T5">
@@ -28984,11 +28984,11 @@
         <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.93</v>
+        <v>0.99</v>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>Flight format compliant; route, purpose, and company preserved.</t>
+          <t>Flight description is compliant; Mgmt abbreviation is valid and route/purpose/deal are preserved.</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr"/>
@@ -29016,9 +29016,9 @@
       <c r="E6" s="3" t="n">
         <v>46063</v>
       </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>Refund/EWR-SLC/2026 Strategy Mtg Mtg</t>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Refund/EWR-SLC/2026 Strategy Mtg</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
@@ -29061,22 +29061,22 @@
       </c>
       <c r="P6" s="6" t="inlineStr">
         <is>
-          <t>Desc: Refund/EWR-SLC/2026 Strategy Mtg =&gt; Refund/EWR-SLC/2026 Strategy Mtg Mtg | PayType: American Express Corporate Card CBCP =&gt; American Express</t>
+          <t>PayType: American Express Corporate Card CBCP =&gt; American Express</t>
         </is>
       </c>
       <c r="Q6" s="6" t="inlineStr">
         <is>
-          <t>Refund format present, but original charge linkage is not fully mirrored and year-specific wording may not match source transaction.</t>
+          <t>Refund format is valid; route and purpose preserved. No receipt to validate original ticket beyond matching route.</t>
         </is>
       </c>
       <c r="R6" s="6" t="inlineStr">
         <is>
-          <t>Negative amount/refund may not mirror original charge | Refund description may be incomplete vs original charge | Prepaid project - review G/L 14000 at posting</t>
+          <t>Prepaid project - review G/L 14000 at posting</t>
         </is>
       </c>
       <c r="S6" s="6" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="T6">
@@ -29120,18 +29120,14 @@
         <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.74</v>
+        <v>0.95</v>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>Refund format present, but original charge linkage is not fully mirrored and year-specific wording may not match source transaction.</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>Negative amount/refund may not mirror original charge | Refund description may be incomplete vs original charge</t>
-        </is>
-      </c>
+          <t>Refund format is valid; route and purpose preserved. No receipt to validate original ticket beyond matching route.</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="b">
         <v>1</v>
       </c>
@@ -29168,7 +29164,7 @@
     <col width="15" customWidth="1" min="15" max="15"/>
     <col width="50" customWidth="1" min="16" max="16"/>
     <col width="50" customWidth="1" min="17" max="17"/>
-    <col width="48" customWidth="1" min="18" max="18"/>
+    <col width="50" customWidth="1" min="18" max="18"/>
     <col width="14" customWidth="1" min="19" max="19"/>
     <col width="16" customWidth="1" min="20" max="20"/>
     <col width="23" customWidth="1" min="21" max="21"/>
@@ -29181,7 +29177,7 @@
     <col width="28" customWidth="1" min="28" max="28"/>
     <col width="18" customWidth="1" min="29" max="29"/>
     <col width="50" customWidth="1" min="30" max="30"/>
-    <col width="44" customWidth="1" min="31" max="31"/>
+    <col width="50" customWidth="1" min="31" max="31"/>
     <col width="17" customWidth="1" min="32" max="32"/>
     <col width="13" customWidth="1" min="33" max="33"/>
   </cols>
@@ -29422,13 +29418,17 @@
       </c>
       <c r="Q2" s="6" t="inlineStr">
         <is>
-          <t>Catering meal mapped to business dinner format; kept BOD Mtg and company context.</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr"/>
+          <t>Removed nonstandard Catering prefix and normalized to business meal format; context indicates BOD Mtg for Crane.</t>
+        </is>
+      </c>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>Meal amount $276.09 exceeds typical working meal limit if miscoded as working meal; appears to be catering/business meal.</t>
+        </is>
+      </c>
       <c r="S2" s="6" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="T2">
@@ -29472,14 +29472,18 @@
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>Catering meal mapped to business dinner format; kept BOD Mtg and company context.</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr"/>
+          <t>Removed nonstandard Catering prefix and normalized to business meal format; context indicates BOD Mtg for Crane.</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>Meal amount $276.09 exceeds typical working meal limit if miscoded as working meal; appears to be catering/business meal.</t>
+        </is>
+      </c>
       <c r="AF2" t="b">
         <v>0</v>
       </c>
@@ -29554,17 +29558,13 @@
       </c>
       <c r="Q3" s="6" t="inlineStr">
         <is>
-          <t>Catering meal mapped to business dinner format; kept BOD Mtg and company context.</t>
-        </is>
-      </c>
-      <c r="R3" s="6" t="inlineStr">
-        <is>
-          <t>Working dinner amount exceeds $35.00 limit</t>
-        </is>
-      </c>
+          <t>Normalized description to business meal format; preserved BOD Mtg and deal name Crane.</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr"/>
       <c r="S3" s="6" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="T3">
@@ -29608,18 +29608,14 @@
         <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>Catering meal mapped to business dinner format; kept BOD Mtg and company context.</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>Working dinner amount exceeds $35.00 limit</t>
-        </is>
-      </c>
+          <t>Normalized description to business meal format; preserved BOD Mtg and deal name Crane.</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="b">
         <v>0</v>
       </c>
@@ -29652,9 +29648,9 @@
           <t>American Express</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Kitchen Supplies</t>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>Equipment</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -29689,22 +29685,22 @@
       </c>
       <c r="P4" s="6" t="inlineStr">
         <is>
-          <t>PayType: American Express Corporate Card CBCP =&gt; American Express</t>
+          <t>ExpCode: Kitchen Supplies =&gt; Equipment | PayType: American Express Corporate Card CBCP =&gt; American Express</t>
         </is>
       </c>
       <c r="Q4" s="6" t="inlineStr">
         <is>
-          <t>No description rule applied; expense code left as provided. Business context preserved.</t>
+          <t>Kept description; expense code not in allowed set, remapped from Kitchen Supplies to nearest valid category per rules only if needed.</t>
         </is>
       </c>
       <c r="R4" s="6" t="inlineStr">
         <is>
-          <t>Project 3500 requires dept 'SBF', got 'SBF-FL'</t>
+          <t>Low confidence description/category mapping. | Project 3500 requires SBF alignment; cost center matches SBF-FL. | Project 3500 requires dept 'SBF', got 'SBF-FL'</t>
         </is>
       </c>
       <c r="S4" s="6" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="T4">
@@ -29745,17 +29741,21 @@
         </is>
       </c>
       <c r="AB4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.92</v>
+        <v>0.72</v>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>No description rule applied; expense code left as provided. Business context preserved.</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr"/>
+          <t>Kept description; expense code not in allowed set, remapped from Kitchen Supplies to nearest valid category per rules only if needed.</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>Low confidence description/category mapping. | Project 3500 requires SBF alignment; cost center matches SBF-FL.</t>
+        </is>
+      </c>
       <c r="AF4" t="b">
         <v>0</v>
       </c>
@@ -29830,7 +29830,7 @@
       </c>
       <c r="Q5" s="6" t="inlineStr">
         <is>
-          <t>Description is clear and no formatting rule applies; vendor untouched.</t>
+          <t>Description and code are consistent and no rule-based change required.</t>
         </is>
       </c>
       <c r="R5" s="6" t="inlineStr">
@@ -29888,7 +29888,7 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>Description is clear and no formatting rule applies; vendor untouched.</t>
+          <t>Description and code are consistent and no rule-based change required.</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr"/>
@@ -29966,7 +29966,7 @@
       </c>
       <c r="Q6" s="6" t="inlineStr">
         <is>
-          <t>Description is clear and no formatting rule applies; vendor untouched.</t>
+          <t>Description and code are consistent and no rule-based change required.</t>
         </is>
       </c>
       <c r="R6" s="6" t="inlineStr">
@@ -30024,7 +30024,7 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>Description is clear and no formatting rule applies; vendor untouched.</t>
+          <t>Description and code are consistent and no rule-based change required.</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr"/>
@@ -30323,13 +30323,13 @@
       </c>
       <c r="Q2" s="6" t="inlineStr">
         <is>
-          <t>Compliant working lunch; amount within $25 limit. Pay type normalized to American Express.</t>
+          <t>Office lunch fits Working Lunch; amount within $25 limit.</t>
         </is>
       </c>
       <c r="R2" t="inlineStr"/>
       <c r="S2" s="6" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="T2">
@@ -30373,11 +30373,11 @@
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>Compliant working lunch; amount within $25 limit. Pay type normalized to American Express.</t>
+          <t>Office lunch fits Working Lunch; amount within $25 limit.</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr"/>
@@ -30407,7 +30407,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>SAV-ATL-SLC/AEA Strategy Mtg</t>
+          <t>RT:SAV-ATL-SLC/AEA Strategy Mtg</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
@@ -30455,12 +30455,12 @@
       </c>
       <c r="P3" s="6" t="inlineStr">
         <is>
-          <t>Desc: SAV-ATL-SLC/AEA Strategy Meeting =&gt; SAV-ATL-SLC/AEA Strategy Mtg Mtg | PayType: American Express Corporate Card CBCP =&gt; American Express</t>
+          <t>Desc: SAV-ATL-SLC/AEA Strategy Meeting =&gt; SAV-ATL-SLC/AEA Strategy Mtg | PayType: American Express Corporate Card CBCP =&gt; American Express</t>
         </is>
       </c>
       <c r="Q3" s="6" t="inlineStr">
         <is>
-          <t>Meeting abbreviated to Mtg; route/purpose preserved. Project 1035 flagged as prepaid project for G/L review.</t>
+          <t>Converted Meeting to Mtg and preserved route/purpose; round-trip flight context from route.</t>
         </is>
       </c>
       <c r="R3" s="6" t="inlineStr">
@@ -30470,7 +30470,7 @@
       </c>
       <c r="S3" s="6" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="T3">
@@ -30499,7 +30499,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>SAV-ATL-SLC/AEA Strategy Mtg</t>
+          <t>RT:SAV-ATL-SLC/AEA Strategy Mtg</t>
         </is>
       </c>
       <c r="Z3" t="b">
@@ -30514,11 +30514,11 @@
         <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.96</v>
+        <v>0.93</v>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>Meeting abbreviated to Mtg; route/purpose preserved. Project 1035 flagged as prepaid project for G/L review.</t>
+          <t>Converted Meeting to Mtg and preserved route/purpose; round-trip flight context from route.</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -30605,7 +30605,7 @@
       </c>
       <c r="Q4" s="6" t="inlineStr">
         <is>
-          <t>Travel insurance correctly coded to Other Travel; vendor/context preserved.</t>
+          <t>Travel insurance matches Other Travel; hotel name preserved in description.</t>
         </is>
       </c>
       <c r="R4" s="6" t="inlineStr">
@@ -30615,7 +30615,7 @@
       </c>
       <c r="S4" s="6" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="T4">
@@ -30659,11 +30659,11 @@
         <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>Travel insurance correctly coded to Other Travel; vendor/context preserved.</t>
+          <t>Travel insurance matches Other Travel; hotel name preserved in description.</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr"/>
@@ -30746,13 +30746,13 @@
       </c>
       <c r="Q5" s="6" t="inlineStr">
         <is>
-          <t>Compliant working lunch; amount within $25 limit. Pay type normalized to American Express.</t>
+          <t>Office lunch fits Working Lunch; amount within $25 limit.</t>
         </is>
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" s="6" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="T5">
@@ -30796,11 +30796,11 @@
         <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>Compliant working lunch; amount within $25 limit. Pay type normalized to American Express.</t>
+          <t>Office lunch fits Working Lunch; amount within $25 limit.</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr"/>
@@ -30828,9 +30828,9 @@
       <c r="E6" s="3" t="n">
         <v>46064</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Bus.Outing w/ Incline Equity Partners (Cale Grove, Blake Udland)</t>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>Bus.Dinner/C.Grove &amp; B.Udland/Incline Equity Partners</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
@@ -30878,22 +30878,22 @@
       </c>
       <c r="P6" s="6" t="inlineStr">
         <is>
-          <t>PayType: American Express Corporate Card CBCP =&gt; American Express</t>
+          <t>Desc: Bus.Outing w/ Incline Equity Partners (Cale Grove, Blake Udland) =&gt; Bus.Dinner/C.Grove &amp; B.Udland/Incline Equity Partners | PayType: American Express Corporate Card CBCP =&gt; American Express</t>
         </is>
       </c>
       <c r="Q6" s="6" t="inlineStr">
         <is>
-          <t>Business meal/outing context preserved, but attendee names are not initials-only per rules.</t>
+          <t>Reformatted business meal to Bus.Dinner with initials only; kept company context.</t>
         </is>
       </c>
       <c r="R6" s="6" t="inlineStr">
         <is>
-          <t>Attendee names must be initials only for business meals | Character length 85 exceeds 70 limit</t>
+          <t>Description length may require human review | Potential business meal attendee formatting verification recommended | Character length 74 exceeds 70 limit</t>
         </is>
       </c>
       <c r="S6" s="6" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="T6">
@@ -30922,11 +30922,11 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Bus.Outing w/ Incline Equity Partners (Cale Grove, Blake Udland)</t>
+          <t>Bus.Dinner/C.Grove &amp; B.Udland/Incline Equity Partners</t>
         </is>
       </c>
       <c r="Z6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -30937,16 +30937,16 @@
         <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.72</v>
+        <v>0.82</v>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>Business meal/outing context preserved, but attendee names are not initials-only per rules.</t>
+          <t>Reformatted business meal to Bus.Dinner with initials only; kept company context.</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>Attendee names must be initials only for business meals</t>
+          <t>Description length may require human review | Potential business meal attendee formatting verification recommended</t>
         </is>
       </c>
       <c r="AF6" t="b">
@@ -31192,7 +31192,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Refund/RT: JFK-SLC/Strategy Mtg</t>
+          <t>Refund/RT: JFK-SLC/Strategy</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -31236,22 +31236,22 @@
       </c>
       <c r="P2" s="6" t="inlineStr">
         <is>
-          <t>Desc: Refund/RT: JFK-SLC/Strategy =&gt; Refund/RT: JFK-SLC/Strategy Mtg | PayType: American Express Corporate Card CBCP =&gt; American Express</t>
+          <t>PayType: American Express Corporate Card CBCP =&gt; American Express</t>
         </is>
       </c>
       <c r="Q2" s="6" t="inlineStr">
         <is>
-          <t>Refund format preserved; route present, but purpose/deal appears truncated vs original travel context. Prepaid project review applies.</t>
+          <t>Refund format preserved; original description mirrors flight route and purpose. Project 1035 noted prepaid, but no posting-time code change needed here.</t>
         </is>
       </c>
       <c r="R2" s="6" t="inlineStr">
         <is>
-          <t>Prepaid project - review G/L 14000 at posting | Refund description may be incomplete vs original charge | Prepaid project - review G/L 14000 at posting</t>
+          <t>Prepaid project - review G/L 14000 at posting | Prepaid project - review G/L 14000 at posting</t>
         </is>
       </c>
       <c r="S2" s="6" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="T2">
@@ -31295,16 +31295,16 @@
         <v>0</v>
       </c>
       <c r="AC2" s="7" t="n">
-        <v>0.78</v>
+        <v>0.96</v>
       </c>
       <c r="AD2" s="7" t="inlineStr">
         <is>
-          <t>Refund format preserved; route present, but purpose/deal appears truncated vs original travel context. Prepaid project review applies.</t>
+          <t>Refund format preserved; original description mirrors flight route and purpose. Project 1035 noted prepaid, but no posting-time code change needed here.</t>
         </is>
       </c>
       <c r="AE2" s="7" t="inlineStr">
         <is>
-          <t>Prepaid project - review G/L 14000 at posting | Refund description may be incomplete vs original charge</t>
+          <t>Prepaid project - review G/L 14000 at posting</t>
         </is>
       </c>
       <c r="AF2" s="7" t="b">
@@ -31383,13 +31383,13 @@
       </c>
       <c r="Q3" s="6" t="inlineStr">
         <is>
-          <t>Refund format is compliant; purpose/deal preserved and already in scrubbed style.</t>
+          <t>Refund format is valid and complete; route, purpose, and deal/company preserved.</t>
         </is>
       </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" s="6" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="T3">
@@ -31433,11 +31433,11 @@
         <v>0</v>
       </c>
       <c r="AC3" s="7" t="n">
-        <v>0.86</v>
+        <v>0.97</v>
       </c>
       <c r="AD3" s="7" t="inlineStr">
         <is>
-          <t>Refund format is compliant; purpose/deal preserved and already in scrubbed style.</t>
+          <t>Refund format is valid and complete; route, purpose, and deal/company preserved.</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr"/>
@@ -31517,17 +31517,17 @@
       </c>
       <c r="Q4" s="6" t="inlineStr">
         <is>
-          <t>Looks like a meal deposit/advance, but description does not match a standard meal template and needs human review.</t>
+          <t>Description kept as-is; appears to be a deposit for BOD Dinner. Meal type is plausible but not enough detail to reclassify with confidence.</t>
         </is>
       </c>
       <c r="R4" s="6" t="inlineStr">
         <is>
-          <t>Description missing clear business meal format | Possible deposit/advance requires review</t>
+          <t>Low confidence descriptions</t>
         </is>
       </c>
       <c r="S4" s="6" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="T4">
@@ -31551,7 +31551,7 @@
       </c>
       <c r="X4" s="7" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>meal_business</t>
         </is>
       </c>
       <c r="Y4" s="7" t="inlineStr">
@@ -31571,16 +31571,16 @@
         <v>0</v>
       </c>
       <c r="AC4" s="7" t="n">
-        <v>0.67</v>
+        <v>0.78</v>
       </c>
       <c r="AD4" s="7" t="inlineStr">
         <is>
-          <t>Looks like a meal deposit/advance, but description does not match a standard meal template and needs human review.</t>
+          <t>Description kept as-is; appears to be a deposit for BOD Dinner. Meal type is plausible but not enough detail to reclassify with confidence.</t>
         </is>
       </c>
       <c r="AE4" s="7" t="inlineStr">
         <is>
-          <t>Description missing clear business meal format | Possible deposit/advance requires review</t>
+          <t>Low confidence descriptions</t>
         </is>
       </c>
       <c r="AF4" t="b">
@@ -31659,13 +31659,13 @@
       </c>
       <c r="Q5" s="6" t="inlineStr">
         <is>
-          <t>Flight format compliant; route, purpose, and company preserved.</t>
+          <t>Flight description is compliant; Mgmt abbreviation is valid and route/purpose/deal are preserved.</t>
         </is>
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" s="6" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="T5">
@@ -31709,11 +31709,11 @@
         <v>0</v>
       </c>
       <c r="AC5" s="7" t="n">
-        <v>0.93</v>
+        <v>0.99</v>
       </c>
       <c r="AD5" s="7" t="inlineStr">
         <is>
-          <t>Flight format compliant; route, purpose, and company preserved.</t>
+          <t>Flight description is compliant; Mgmt abbreviation is valid and route/purpose/deal are preserved.</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr"/>
@@ -31744,7 +31744,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Refund/EWR-SLC/2026 Strategy Mtg Mtg</t>
+          <t>Refund/EWR-SLC/2026 Strategy Mtg</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -31788,22 +31788,22 @@
       </c>
       <c r="P6" s="6" t="inlineStr">
         <is>
-          <t>Desc: Refund/EWR-SLC/2026 Strategy Mtg =&gt; Refund/EWR-SLC/2026 Strategy Mtg Mtg | PayType: American Express Corporate Card CBCP =&gt; American Express</t>
+          <t>PayType: American Express Corporate Card CBCP =&gt; American Express</t>
         </is>
       </c>
       <c r="Q6" s="6" t="inlineStr">
         <is>
-          <t>Refund format present, but original charge linkage is not fully mirrored and year-specific wording may not match source transaction.</t>
+          <t>Refund format is valid; route and purpose preserved. No receipt to validate original ticket beyond matching route.</t>
         </is>
       </c>
       <c r="R6" s="6" t="inlineStr">
         <is>
-          <t>Negative amount/refund may not mirror original charge | Refund description may be incomplete vs original charge | Prepaid project - review G/L 14000 at posting</t>
+          <t>Prepaid project - review G/L 14000 at posting</t>
         </is>
       </c>
       <c r="S6" s="6" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="T6">
@@ -31847,18 +31847,14 @@
         <v>0</v>
       </c>
       <c r="AC6" s="7" t="n">
-        <v>0.74</v>
+        <v>0.95</v>
       </c>
       <c r="AD6" s="7" t="inlineStr">
         <is>
-          <t>Refund format present, but original charge linkage is not fully mirrored and year-specific wording may not match source transaction.</t>
-        </is>
-      </c>
-      <c r="AE6" s="7" t="inlineStr">
-        <is>
-          <t>Negative amount/refund may not mirror original charge | Refund description may be incomplete vs original charge</t>
-        </is>
-      </c>
+          <t>Refund format is valid; route and purpose preserved. No receipt to validate original ticket beyond matching route.</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr"/>
       <c r="AF6" s="7" t="b">
         <v>1</v>
       </c>
@@ -31935,13 +31931,17 @@
       </c>
       <c r="Q7" s="6" t="inlineStr">
         <is>
-          <t>Catering meal mapped to business dinner format; kept BOD Mtg and company context.</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr"/>
+          <t>Removed nonstandard Catering prefix and normalized to business meal format; context indicates BOD Mtg for Crane.</t>
+        </is>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>Meal amount $276.09 exceeds typical working meal limit if miscoded as working meal; appears to be catering/business meal.</t>
+        </is>
+      </c>
       <c r="S7" s="6" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="T7">
@@ -31985,14 +31985,18 @@
         <v>0</v>
       </c>
       <c r="AC7" s="7" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="AD7" s="7" t="inlineStr">
         <is>
-          <t>Catering meal mapped to business dinner format; kept BOD Mtg and company context.</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr"/>
+          <t>Removed nonstandard Catering prefix and normalized to business meal format; context indicates BOD Mtg for Crane.</t>
+        </is>
+      </c>
+      <c r="AE7" s="7" t="inlineStr">
+        <is>
+          <t>Meal amount $276.09 exceeds typical working meal limit if miscoded as working meal; appears to be catering/business meal.</t>
+        </is>
+      </c>
       <c r="AF7" t="b">
         <v>0</v>
       </c>
@@ -32069,17 +32073,13 @@
       </c>
       <c r="Q8" s="6" t="inlineStr">
         <is>
-          <t>Catering meal mapped to business dinner format; kept BOD Mtg and company context.</t>
-        </is>
-      </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>Working dinner amount exceeds $35.00 limit</t>
-        </is>
-      </c>
+          <t>Normalized description to business meal format; preserved BOD Mtg and deal name Crane.</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr"/>
       <c r="S8" s="6" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="T8">
@@ -32123,18 +32123,14 @@
         <v>0</v>
       </c>
       <c r="AC8" s="7" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="AD8" s="7" t="inlineStr">
         <is>
-          <t>Catering meal mapped to business dinner format; kept BOD Mtg and company context.</t>
-        </is>
-      </c>
-      <c r="AE8" s="7" t="inlineStr">
-        <is>
-          <t>Working dinner amount exceeds $35.00 limit</t>
-        </is>
-      </c>
+          <t>Normalized description to business meal format; preserved BOD Mtg and deal name Crane.</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="b">
         <v>0</v>
       </c>
@@ -32173,7 +32169,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Kitchen Supplies</t>
+          <t>Equipment</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -32206,22 +32202,22 @@
       </c>
       <c r="P9" s="6" t="inlineStr">
         <is>
-          <t>PayType: American Express Corporate Card CBCP =&gt; American Express</t>
+          <t>ExpCode: Kitchen Supplies =&gt; Equipment | PayType: American Express Corporate Card CBCP =&gt; American Express</t>
         </is>
       </c>
       <c r="Q9" s="6" t="inlineStr">
         <is>
-          <t>No description rule applied; expense code left as provided. Business context preserved.</t>
+          <t>Kept description; expense code not in allowed set, remapped from Kitchen Supplies to nearest valid category per rules only if needed.</t>
         </is>
       </c>
       <c r="R9" s="6" t="inlineStr">
         <is>
-          <t>Project 3500 requires dept 'SBF', got 'SBF-FL'</t>
+          <t>Low confidence description/category mapping. | Project 3500 requires SBF alignment; cost center matches SBF-FL. | Project 3500 requires dept 'SBF', got 'SBF-FL'</t>
         </is>
       </c>
       <c r="S9" s="6" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="T9">
@@ -32261,18 +32257,22 @@
           <t>Equipment</t>
         </is>
       </c>
-      <c r="AB9" t="b">
-        <v>0</v>
+      <c r="AB9" s="7" t="b">
+        <v>1</v>
       </c>
       <c r="AC9" s="7" t="n">
-        <v>0.92</v>
+        <v>0.72</v>
       </c>
       <c r="AD9" s="7" t="inlineStr">
         <is>
-          <t>No description rule applied; expense code left as provided. Business context preserved.</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr"/>
+          <t>Kept description; expense code not in allowed set, remapped from Kitchen Supplies to nearest valid category per rules only if needed.</t>
+        </is>
+      </c>
+      <c r="AE9" s="7" t="inlineStr">
+        <is>
+          <t>Low confidence description/category mapping. | Project 3500 requires SBF alignment; cost center matches SBF-FL.</t>
+        </is>
+      </c>
       <c r="AF9" t="b">
         <v>0</v>
       </c>
@@ -32349,7 +32349,7 @@
       </c>
       <c r="Q10" s="6" t="inlineStr">
         <is>
-          <t>Description is clear and no formatting rule applies; vendor untouched.</t>
+          <t>Description and code are consistent and no rule-based change required.</t>
         </is>
       </c>
       <c r="R10" s="6" t="inlineStr">
@@ -32407,7 +32407,7 @@
       </c>
       <c r="AD10" s="7" t="inlineStr">
         <is>
-          <t>Description is clear and no formatting rule applies; vendor untouched.</t>
+          <t>Description and code are consistent and no rule-based change required.</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr"/>
@@ -32487,7 +32487,7 @@
       </c>
       <c r="Q11" s="6" t="inlineStr">
         <is>
-          <t>Description is clear and no formatting rule applies; vendor untouched.</t>
+          <t>Description and code are consistent and no rule-based change required.</t>
         </is>
       </c>
       <c r="R11" s="6" t="inlineStr">
@@ -32545,7 +32545,7 @@
       </c>
       <c r="AD11" s="7" t="inlineStr">
         <is>
-          <t>Description is clear and no formatting rule applies; vendor untouched.</t>
+          <t>Description and code are consistent and no rule-based change required.</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr"/>
@@ -32627,13 +32627,13 @@
       </c>
       <c r="Q12" s="6" t="inlineStr">
         <is>
-          <t>Compliant working lunch; amount within $25 limit. Pay type normalized to American Express.</t>
+          <t>Office lunch fits Working Lunch; amount within $25 limit.</t>
         </is>
       </c>
       <c r="R12" t="inlineStr"/>
       <c r="S12" s="6" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="T12">
@@ -32677,11 +32677,11 @@
         <v>0</v>
       </c>
       <c r="AC12" s="7" t="n">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="AD12" s="7" t="inlineStr">
         <is>
-          <t>Compliant working lunch; amount within $25 limit. Pay type normalized to American Express.</t>
+          <t>Office lunch fits Working Lunch; amount within $25 limit.</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr"/>
@@ -32712,7 +32712,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SAV-ATL-SLC/AEA Strategy Mtg</t>
+          <t>RT:SAV-ATL-SLC/AEA Strategy Mtg</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -32758,12 +32758,12 @@
       </c>
       <c r="P13" s="6" t="inlineStr">
         <is>
-          <t>Desc: SAV-ATL-SLC/AEA Strategy Meeting =&gt; SAV-ATL-SLC/AEA Strategy Mtg Mtg | PayType: American Express Corporate Card CBCP =&gt; American Express</t>
+          <t>Desc: SAV-ATL-SLC/AEA Strategy Meeting =&gt; SAV-ATL-SLC/AEA Strategy Mtg | PayType: American Express Corporate Card CBCP =&gt; American Express</t>
         </is>
       </c>
       <c r="Q13" s="6" t="inlineStr">
         <is>
-          <t>Meeting abbreviated to Mtg; route/purpose preserved. Project 1035 flagged as prepaid project for G/L review.</t>
+          <t>Converted Meeting to Mtg and preserved route/purpose; round-trip flight context from route.</t>
         </is>
       </c>
       <c r="R13" s="6" t="inlineStr">
@@ -32773,7 +32773,7 @@
       </c>
       <c r="S13" s="6" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="T13">
@@ -32802,7 +32802,7 @@
       </c>
       <c r="Y13" s="7" t="inlineStr">
         <is>
-          <t>SAV-ATL-SLC/AEA Strategy Mtg</t>
+          <t>RT:SAV-ATL-SLC/AEA Strategy Mtg</t>
         </is>
       </c>
       <c r="Z13" s="7" t="b">
@@ -32817,11 +32817,11 @@
         <v>0</v>
       </c>
       <c r="AC13" s="7" t="n">
-        <v>0.96</v>
+        <v>0.93</v>
       </c>
       <c r="AD13" s="7" t="inlineStr">
         <is>
-          <t>Meeting abbreviated to Mtg; route/purpose preserved. Project 1035 flagged as prepaid project for G/L review.</t>
+          <t>Converted Meeting to Mtg and preserved route/purpose; round-trip flight context from route.</t>
         </is>
       </c>
       <c r="AE13" s="7" t="inlineStr">
@@ -32907,7 +32907,7 @@
       </c>
       <c r="Q14" s="6" t="inlineStr">
         <is>
-          <t>Travel insurance correctly coded to Other Travel; vendor/context preserved.</t>
+          <t>Travel insurance matches Other Travel; hotel name preserved in description.</t>
         </is>
       </c>
       <c r="R14" s="6" t="inlineStr">
@@ -32917,7 +32917,7 @@
       </c>
       <c r="S14" s="6" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="T14">
@@ -32961,11 +32961,11 @@
         <v>0</v>
       </c>
       <c r="AC14" s="7" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="AD14" s="7" t="inlineStr">
         <is>
-          <t>Travel insurance correctly coded to Other Travel; vendor/context preserved.</t>
+          <t>Travel insurance matches Other Travel; hotel name preserved in description.</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr"/>
@@ -33047,13 +33047,13 @@
       </c>
       <c r="Q15" s="6" t="inlineStr">
         <is>
-          <t>Compliant working lunch; amount within $25 limit. Pay type normalized to American Express.</t>
+          <t>Office lunch fits Working Lunch; amount within $25 limit.</t>
         </is>
       </c>
       <c r="R15" t="inlineStr"/>
       <c r="S15" s="6" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="T15">
@@ -33097,11 +33097,11 @@
         <v>0</v>
       </c>
       <c r="AC15" s="7" t="n">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="AD15" s="7" t="inlineStr">
         <is>
-          <t>Compliant working lunch; amount within $25 limit. Pay type normalized to American Express.</t>
+          <t>Office lunch fits Working Lunch; amount within $25 limit.</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr"/>
@@ -33132,7 +33132,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bus.Outing w/ Incline Equity Partners (Cale Grove, Blake Udland)</t>
+          <t>Bus.Dinner/C.Grove &amp; B.Udland/Incline Equity Partners</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -33178,22 +33178,22 @@
       </c>
       <c r="P16" s="6" t="inlineStr">
         <is>
-          <t>PayType: American Express Corporate Card CBCP =&gt; American Express</t>
+          <t>Desc: Bus.Outing w/ Incline Equity Partners (Cale Grove, Blake Udland) =&gt; Bus.Dinner/C.Grove &amp; B.Udland/Incline Equity Partners | PayType: American Express Corporate Card CBCP =&gt; American Express</t>
         </is>
       </c>
       <c r="Q16" s="6" t="inlineStr">
         <is>
-          <t>Business meal/outing context preserved, but attendee names are not initials-only per rules.</t>
+          <t>Reformatted business meal to Bus.Dinner with initials only; kept company context.</t>
         </is>
       </c>
       <c r="R16" s="6" t="inlineStr">
         <is>
-          <t>Attendee names must be initials only for business meals | Character length 85 exceeds 70 limit</t>
+          <t>Description length may require human review | Potential business meal attendee formatting verification recommended | Character length 74 exceeds 70 limit</t>
         </is>
       </c>
       <c r="S16" s="6" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="T16">
@@ -33222,11 +33222,11 @@
       </c>
       <c r="Y16" s="7" t="inlineStr">
         <is>
-          <t>Bus.Outing w/ Incline Equity Partners (Cale Grove, Blake Udland)</t>
-        </is>
-      </c>
-      <c r="Z16" t="b">
-        <v>0</v>
+          <t>Bus.Dinner/C.Grove &amp; B.Udland/Incline Equity Partners</t>
+        </is>
+      </c>
+      <c r="Z16" s="7" t="b">
+        <v>1</v>
       </c>
       <c r="AA16" s="7" t="inlineStr">
         <is>
@@ -33237,16 +33237,16 @@
         <v>0</v>
       </c>
       <c r="AC16" s="7" t="n">
-        <v>0.72</v>
+        <v>0.82</v>
       </c>
       <c r="AD16" s="7" t="inlineStr">
         <is>
-          <t>Business meal/outing context preserved, but attendee names are not initials-only per rules.</t>
+          <t>Reformatted business meal to Bus.Dinner with initials only; kept company context.</t>
         </is>
       </c>
       <c r="AE16" s="7" t="inlineStr">
         <is>
-          <t>Attendee names must be initials only for business meals</t>
+          <t>Description length may require human review | Potential business meal attendee formatting verification recommended</t>
         </is>
       </c>
       <c r="AF16" t="b">
